--- a/tests/workbooktests/workbooks/test_settings.xlsx
+++ b/tests/workbooktests/workbooks/test_settings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36706E9D-00AE-462D-BFD6-D70E2F2D677F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41F476E-159A-4CFC-A186-A44FB6D36335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{4A4E2BF8-2237-4B7A-8724-C72F5F3DA83A}"/>
+    <workbookView xWindow="3585" yWindow="-19050" windowWidth="30690" windowHeight="16530" xr2:uid="{4A4E2BF8-2237-4B7A-8724-C72F5F3DA83A}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="17">
   <si>
     <t>EvaluationDate</t>
   </si>
@@ -106,6 +106,12 @@
   </si>
   <si>
     <t>qlSettingsResetEvaluationDate</t>
+  </si>
+  <si>
+    <t>EnforcesTodaysHistoricFixings (Reset)</t>
+  </si>
+  <si>
+    <t>IncludeReferenceDateEvents (Reset)</t>
   </si>
 </sst>
 </file>
@@ -141,9 +147,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1103CA6-660F-4EF7-9FA5-FD7A1BE97203}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.33203125" customWidth="1"/>
@@ -524,7 +531,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="b" cm="1">
-        <f t="array" ref="B6">_xll.qlSettingsSetEnforcesTodaysHistoricFixings(B5)</f>
+        <f t="array" ref="B6">_xll.qlSettingsSetEnforcesTodaysHistoricFixings(B5,B2)</f>
         <v>1</v>
       </c>
     </row>
@@ -537,110 +544,188 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B9" t="b" cm="1">
+        <f t="array" ref="B9">_xll.qlSettingsSetEnforcesTodaysHistoricFixings(B8,B7)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B10" t="b" cm="1">
-        <f t="array" ref="B10">_xll.qlSettingsSetIncludeReferenceDateEvents(B9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="b" cm="1">
-        <f t="array" ref="B11">_xll.qlSettingsGetIncludeReferenceDateEvents(B10)</f>
+        <f t="array" ref="B10">_xll.qlSettingsGetEnforcesTodaysHistoricFixings(B9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="b">
+        <v>6</v>
+      </c>
+      <c r="B13" t="b" cm="1">
+        <f t="array" ref="B13">_xll.qlSettingsSetIncludeReferenceDateEvents(B12,B2)</f>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" t="b" cm="1">
-        <f t="array" ref="B14">_xll.qlSettingsSetIncludeTodaysCashFlows(B13)</f>
+        <f t="array" ref="B14">_xll.qlSettingsGetIncludeReferenceDateEvents(B13)</f>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="b" cm="1">
+        <f t="array" ref="B16">_xll.qlSettingsSetIncludeReferenceDateEvents(B15,B14)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="b" cm="1">
+        <f t="array" ref="B17">_xll.qlSettingsGetIncludeReferenceDateEvents(B16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="b" cm="1">
+        <f t="array" ref="B20">_xll.qlSettingsSetIncludeTodaysCashFlows(B19,B2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B15" t="b" cm="1">
-        <f t="array" ref="B15">_xll.qlSettingsGetIncludeTodaysCashFlows(B14)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B21" t="b" cm="1">
+        <f t="array" ref="B21">_xll.qlSettingsGetIncludeTodaysCashFlows(B20)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="b" cm="1">
+        <f t="array" ref="B23">_xll.qlSettingsSetIncludeTodaysCashFlows(B22,B21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" t="b" cm="1">
+        <f t="array" ref="B24">_xll.qlSettingsGetIncludeTodaysCashFlows(B23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B26" s="1">
         <f>B3+365</f>
         <v>44197</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="1" cm="1">
-        <f t="array" ref="B19">_xll.qlSettingsSetEvaluationDate(B18)</f>
+      <c r="B27" s="1" cm="1">
+        <f t="array" ref="B27">_xll.qlSettingsSetEvaluationDate(B26)</f>
         <v>44197</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="1" cm="1">
-        <f t="array" ref="B20">_xll.qlSettingsGetEvaluationDate(B19)</f>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" cm="1">
+        <f t="array" ref="B28">_xll.qlSettingsGetEvaluationDate(B27)</f>
         <v>44197</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="1" cm="1">
-        <f t="array" ref="B21">_xll.qlSettingsResetEvaluationDate(B20)</f>
-        <v>46165</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22" s="1" cm="1">
-        <f t="array" ref="B22">_xll.qlSettingsGetEvaluationDate(B21)</f>
-        <v>46165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B29" s="1" cm="1">
+        <f t="array" ref="B29">_xll.qlSettingsResetEvaluationDate(B28)</f>
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="1" cm="1">
+        <f t="array" ref="B30">_xll.qlSettingsGetEvaluationDate(B29)</f>
+        <v>46231</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="1" cm="1">
-        <f t="array" ref="B24">_xll.qlSettingsAnchorEvaluationDate(B22)</f>
-        <v>46165</v>
+      <c r="B32" s="1" cm="1">
+        <f t="array" ref="B32">_xll.qlSettingsAnchorEvaluationDate(B30)</f>
+        <v>46231</v>
       </c>
     </row>
   </sheetData>
